--- a/results/表2_水分浓度.xlsx
+++ b/results/表2_水分浓度.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -639,7 +639,7 @@
     <row r="1" ht="14.1" customHeight="1" s="4">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>时间\到药材中心的距离</t>
+          <t>时间/s\到药材中心的距离/cm</t>
         </is>
       </c>
       <c r="B1" s="1" t="n">
@@ -675,7 +675,7 @@
         <v>2.55</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2.27016</v>
+        <v>2.2466</v>
       </c>
     </row>
     <row r="3" ht="14.1" customHeight="1" s="4">
@@ -692,10 +692,10 @@
         <v>2.55</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2.54918</v>
+        <v>2.5492</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>2.07293</v>
+        <v>2.0507</v>
       </c>
     </row>
     <row r="4" ht="14.1" customHeight="1" s="4">
@@ -709,13 +709,13 @@
         <v>2.55</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2.54999</v>
+        <v>2.55</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.53521</v>
+        <v>2.5352</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.89803</v>
+        <v>1.8769</v>
       </c>
     </row>
     <row r="5" ht="14.1" customHeight="1" s="4">
@@ -729,13 +729,13 @@
         <v>2.55</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2.54968</v>
+        <v>2.5497</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.50446</v>
+        <v>2.5045</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.77505</v>
+        <v>1.7547</v>
       </c>
     </row>
     <row r="6">
@@ -746,16 +746,16 @@
         <v>2.55</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2.54999</v>
+        <v>2.55</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.54817</v>
+        <v>2.5482</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.46449</v>
+        <v>2.4645</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.67832</v>
+        <v>1.6585</v>
       </c>
     </row>
     <row r="7">
@@ -766,16 +766,16 @@
         <v>2.55</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2.54994</v>
+        <v>2.5499</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2.54452</v>
+        <v>2.5445</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.42053</v>
+        <v>2.4205</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.59801</v>
+        <v>1.5787</v>
       </c>
     </row>
     <row r="8">
@@ -783,19 +783,19 @@
         <v>1800</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2.54999</v>
+        <v>2.55</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2.54972</v>
+        <v>2.5497</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2.53827</v>
+        <v>2.5383</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>2.3754</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.52912</v>
+        <v>1.5102</v>
       </c>
     </row>
   </sheetData>
